--- a/target/classes/emails.xlsx
+++ b/target/classes/emails.xlsx
@@ -16,369 +16,609 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>Email ID's</t>
   </si>
   <si>
-    <t xml:space="preserve">akshay.jith@people-click.com </t>
-  </si>
-  <si>
-    <t xml:space="preserve">akshay.s@imcsgroup.net </t>
-  </si>
-  <si>
-    <t>akshay@cogdual.com</t>
-  </si>
-  <si>
-    <t>akshita.agarwal@ranosys.com</t>
-  </si>
-  <si>
-    <t>akshita.epochfolio@gmail.com</t>
-  </si>
-  <si>
-    <t>akshita.singh@partnr.in</t>
-  </si>
-  <si>
-    <t>Akshita@buzzhire.in</t>
-  </si>
-  <si>
-    <t>akshithas@princetonamerica.com</t>
-  </si>
-  <si>
-    <t>alekhya@uniquehire.com</t>
-  </si>
-  <si>
-    <t>alina.zaman@girikon.com</t>
-  </si>
-  <si>
-    <t>aliya.u@pattemdigital.com</t>
-  </si>
-  <si>
-    <t>Aliya@xanikainfotech.com</t>
-  </si>
-  <si>
-    <t>allu@finessedirect.com</t>
-  </si>
-  <si>
-    <t>aman.shrivastava@vvdntech.in</t>
-  </si>
-  <si>
-    <t>aman.verma@impactqa.com</t>
-  </si>
-  <si>
-    <t>amarnadh.b@uniquehire.com</t>
-  </si>
-  <si>
-    <t>Amatullah@krayr.in</t>
-  </si>
-  <si>
-    <t>amee.hr.hi@gmail.com</t>
-  </si>
-  <si>
-    <t>amita@sourcebae.com</t>
-  </si>
-  <si>
-    <t>amrita@rudrainnovative.com</t>
-  </si>
-  <si>
-    <t>Amrutha.m@sbs-global.com</t>
-  </si>
-  <si>
-    <t>amudiraj@qti.qualcomm.com</t>
-  </si>
-  <si>
-    <t>amulya.gunda@atyeti.com</t>
-  </si>
-  <si>
-    <t>anagandula.manasa@in.experis.com</t>
-  </si>
-  <si>
-    <t>anamika@netquo.in</t>
-  </si>
-  <si>
-    <t>anamika@provaantech.com</t>
-  </si>
-  <si>
-    <t>anand.kumarpandey@hcltech.com</t>
-  </si>
-  <si>
-    <t>anand.p@otomeyt.ai</t>
-  </si>
-  <si>
-    <t>anandp@onetick.in</t>
-  </si>
-  <si>
-    <t>ananya.pandit@primaryio.com</t>
-  </si>
-  <si>
-    <t>ananya@nilasu.com</t>
-  </si>
-  <si>
-    <t>anchal.malhotra@graymatrix.com</t>
-  </si>
-  <si>
-    <t>Anchal@beansbit.com</t>
-  </si>
-  <si>
-    <t>ancy.s@saasvaap.com</t>
-  </si>
-  <si>
-    <t>Aneri.thakkar@admedia.com</t>
-  </si>
-  <si>
-    <t>angeline@codersbrain.com</t>
-  </si>
-  <si>
-    <t>anisha.sharma@reqpedia.com</t>
-  </si>
-  <si>
-    <t>anishbivalkar@gmail.com</t>
-  </si>
-  <si>
-    <t>Anita.singh@apolisindia.com</t>
-  </si>
-  <si>
-    <t>anitha@adroitinnovative.com</t>
-  </si>
-  <si>
-    <t>anjali.d@techbrainz.com</t>
-  </si>
-  <si>
-    <t>anjali.kandpal@devg.org</t>
-  </si>
-  <si>
-    <t>anjali.singh@devlabstechnology.com</t>
-  </si>
-  <si>
-    <t>Anjali@idah-tech.com</t>
-  </si>
-  <si>
-    <t>anjali@prorsum-tech.com</t>
-  </si>
-  <si>
-    <t>anjali_verma@42works.net</t>
-  </si>
-  <si>
-    <t>anju.kushwaha@antino.com</t>
-  </si>
-  <si>
-    <t>anjuk1@hexaware.com</t>
-  </si>
-  <si>
-    <t>anjum@binqle.com</t>
-  </si>
-  <si>
-    <t>ank.salesteam@gmail.com</t>
-  </si>
-  <si>
-    <t>ankit.a@bluemojosolutions.com</t>
-  </si>
-  <si>
-    <t>ankit@purplebox.co.in</t>
-  </si>
-  <si>
-    <t>ankita.g@zelusindia.com</t>
-  </si>
-  <si>
-    <t>ankita.ghorai@verinite.com</t>
-  </si>
-  <si>
-    <t>ankita.goyal@rhatechnologies.com</t>
-  </si>
-  <si>
-    <t>ankita.rathod@realworldhr.in</t>
-  </si>
-  <si>
-    <t>ankita.sharma@testingxperts.com</t>
-  </si>
-  <si>
-    <t>ankita@saibullglobal.com</t>
-  </si>
-  <si>
-    <t>ankita@teknobit.com</t>
-  </si>
-  <si>
-    <t>ankush.chandra@covetus.com</t>
-  </si>
-  <si>
-    <t>anmol.khosla@appzlogic.com</t>
-  </si>
-  <si>
-    <t>anshika.k@agitss.in</t>
-  </si>
-  <si>
-    <t>anshu.mittal@crestechsoftware.com</t>
-  </si>
-  <si>
-    <t>anshul.gaikwad@onixnet.us</t>
-  </si>
-  <si>
-    <t>anu.mittal@testingxperts.com</t>
-  </si>
-  <si>
-    <t>anubha.jain@jinendrainfotech.in</t>
-  </si>
-  <si>
-    <t>anuhya.arani@infobellit.com</t>
-  </si>
-  <si>
-    <t>anuja@prodt.co</t>
-  </si>
-  <si>
-    <t>anumalika.s@twsol.com</t>
-  </si>
-  <si>
-    <t>anupama.sharma@roinet.in</t>
-  </si>
-  <si>
-    <t>anurags@cloverbridgetech.com</t>
-  </si>
-  <si>
-    <t>anusha.bodeddula@sparshcom.net</t>
-  </si>
-  <si>
-    <t>anusha.i@3shooltech.com</t>
-  </si>
-  <si>
-    <t>anushka.rajput@anciledigital.com</t>
-  </si>
-  <si>
-    <t>anushka.saxena.mba@gmail.com</t>
-  </si>
-  <si>
-    <t>anushreeconverse@gmail.com</t>
-  </si>
-  <si>
-    <t>anveeth.mallya@envsage.com</t>
-  </si>
-  <si>
-    <t>anwesha.roy@moolya.com</t>
-  </si>
-  <si>
-    <t>ApplicantAccommodations@gartner.com</t>
-  </si>
-  <si>
-    <t>Apply@innovaitglobal.com</t>
-  </si>
-  <si>
-    <t>aquib.sohail@360degreecloud.com</t>
-  </si>
-  <si>
-    <t>arathi@tech-beam.com</t>
-  </si>
-  <si>
-    <t>aravinth.g@codingmart.com</t>
-  </si>
-  <si>
-    <t>archana.dubey@harjai.com</t>
-  </si>
-  <si>
-    <t>archana.ka@peoplefy.com</t>
-  </si>
-  <si>
-    <t>archi.aggarwal@innovationm.com</t>
-  </si>
-  <si>
-    <t>arjun.u@ziniosedge.com</t>
-  </si>
-  <si>
-    <t>arnab.bakshi@ascendion.com</t>
-  </si>
-  <si>
-    <t>arnika.gangwar@xponentiums.com</t>
-  </si>
-  <si>
-    <t>arnika_wadhawan@epam.com</t>
-  </si>
-  <si>
-    <t>arpita.s@phitechlabs.com</t>
-  </si>
-  <si>
-    <t>arsalan@ztekinc.com</t>
-  </si>
-  <si>
-    <t>Arshad.Ar_ext@Ltts.com</t>
-  </si>
-  <si>
-    <t>Arshad.cg360@gmail.com</t>
-  </si>
-  <si>
-    <t>arshad.sheikh@zuplon.com</t>
-  </si>
-  <si>
-    <t>arshaik@appstekcorp.com</t>
-  </si>
-  <si>
-    <t>arshi@shareindia.com</t>
-  </si>
-  <si>
-    <t>arti.jha@orcapod.work</t>
-  </si>
-  <si>
-    <t>arun.kumar@alchemytechsol.com</t>
-  </si>
-  <si>
-    <t>arya.k@tekitsolution.com</t>
-  </si>
-  <si>
-    <t>arya@carbike360.com</t>
-  </si>
-  <si>
-    <t>Aryaanshi.c@apideltech.com</t>
-  </si>
-  <si>
-    <t>aryan@sparixglobal.com</t>
-  </si>
-  <si>
-    <t>asawari.sharangdhar@crescendogroup.in</t>
-  </si>
-  <si>
-    <t>Ashika.shaik@signitives.net</t>
-  </si>
-  <si>
-    <t>Ashish.k@innovise-it.com</t>
-  </si>
-  <si>
-    <t>ashish.kumar@cubastion.com</t>
-  </si>
-  <si>
-    <t>ashish.t@stratosphere.co.in</t>
-  </si>
-  <si>
-    <t>ashish@softovista.com</t>
-  </si>
-  <si>
-    <t>ashish_k@theedgepartnership.com</t>
-  </si>
-  <si>
-    <t>ashok.m@macronix.in</t>
-  </si>
-  <si>
-    <t>Ashutosh.singh@saivasystem.com</t>
-  </si>
-  <si>
-    <t>ashutosh.singh@veridicsolutions.com</t>
-  </si>
-  <si>
-    <t>ashwani.c@smartedgesolutions.co.uk</t>
-  </si>
-  <si>
-    <t>ashwin.bhagat.profile@gmail.com</t>
-  </si>
-  <si>
-    <t>asritha.peddi@olooptech.com</t>
-  </si>
-  <si>
-    <t>astha@hyresnap.com</t>
-  </si>
-  <si>
-    <t>aswani.v@tachyontech.com</t>
-  </si>
-  <si>
-    <t>aswathy.s@flycatchtech.com</t>
-  </si>
-  <si>
-    <t>atharva.vispute@appzlogic.com</t>
+    <t>atithi@talentaura.in</t>
+  </si>
+  <si>
+    <t>atul.kumar1@aptaracorp.com</t>
+  </si>
+  <si>
+    <t>Atul.saini@esscorptech.com</t>
+  </si>
+  <si>
+    <t>atvidhusha.vs@visionyle.com</t>
+  </si>
+  <si>
+    <t>avenjala.fernando@firstcron.com</t>
+  </si>
+  <si>
+    <t>averma1@vbeyondapac.com</t>
+  </si>
+  <si>
+    <t>avisha.singh@lancesoft.in</t>
+  </si>
+  <si>
+    <t>avninder.singh@peopleintegra.com</t>
+  </si>
+  <si>
+    <t>avpdnyaneshwari@gmail.com</t>
+  </si>
+  <si>
+    <t>ayesha@lltech.in</t>
+  </si>
+  <si>
+    <t>Ayushi.patel@anciledigital.com</t>
+  </si>
+  <si>
+    <t>ayushi.vashisht@traqo.io</t>
+  </si>
+  <si>
+    <t>ayushi@mercuriusipl.com</t>
+  </si>
+  <si>
+    <t>ayushi@nexusprofessionals.in</t>
+  </si>
+  <si>
+    <t>ayyadav@deqode.com</t>
+  </si>
+  <si>
+    <t>azat@proof-8.com</t>
+  </si>
+  <si>
+    <t>azmathulla.shaik@codejugar.com</t>
+  </si>
+  <si>
+    <t>azrath.k@tachyontech.com</t>
+  </si>
+  <si>
+    <t>b62677057@gmail.com</t>
+  </si>
+  <si>
+    <t>babita@techmavesoftware.com</t>
+  </si>
+  <si>
+    <t>babu.v@melayati.com</t>
+  </si>
+  <si>
+    <t>balamurali_krishna@epam.com</t>
+  </si>
+  <si>
+    <t>balasree.j@kanarystaffing.com</t>
+  </si>
+  <si>
+    <t>bandapalli.sarada@cantiktech.com</t>
+  </si>
+  <si>
+    <t>bansi.nsg@outlook.com</t>
+  </si>
+  <si>
+    <t>barsha.pattnaik@srijanspectrum.com</t>
+  </si>
+  <si>
+    <t>bbasavaraju@ciberspring.com</t>
+  </si>
+  <si>
+    <t>Beera.sushma@quesscorp.com</t>
+  </si>
+  <si>
+    <t>benfield@xanikainfotech.com</t>
+  </si>
+  <si>
+    <t>bhagyashri@ziventra.com</t>
+  </si>
+  <si>
+    <t>bharaneej@maveric-systems.com</t>
+  </si>
+  <si>
+    <t>bharath.k@intellectt.com</t>
+  </si>
+  <si>
+    <t>bharath@datanetiix.com</t>
+  </si>
+  <si>
+    <t>bhargav.i@tachyontech.com</t>
+  </si>
+  <si>
+    <t>bhargavi.b@palni.com</t>
+  </si>
+  <si>
+    <t>bhargavi.kulkarni@fidelistech.com</t>
+  </si>
+  <si>
+    <t>bhargavi@icsglobalsoft.com</t>
+  </si>
+  <si>
+    <t>bhargaviteja@edurungroup.in</t>
+  </si>
+  <si>
+    <t>bharti.choudhary1@comviva.com</t>
+  </si>
+  <si>
+    <t>bhaskarbhaskar111v@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavana.andanapalli@enfec.com</t>
+  </si>
+  <si>
+    <t>bhavana.softomatic@gmail.com</t>
+  </si>
+  <si>
+    <t>bhavanak@vilwaatech.com</t>
+  </si>
+  <si>
+    <t>bhavin.parekh@anciledigital.com</t>
+  </si>
+  <si>
+    <t>bhavna.upadhyay@exchimious.com</t>
+  </si>
+  <si>
+    <t>bhavya@intellious.tech</t>
+  </si>
+  <si>
+    <t>bhawana.anand@uniquehirings.in</t>
+  </si>
+  <si>
+    <t>bhoopathyraja.ravindran@ust.com</t>
+  </si>
+  <si>
+    <t>bhuvana@prorsum-tech.com</t>
+  </si>
+  <si>
+    <t>bhuvaneswarir@maveric-systems.com</t>
+  </si>
+  <si>
+    <t>bhuvi.gupta@publicissapient.com</t>
+  </si>
+  <si>
+    <t>bhuwan.purohit@scrobits.com</t>
+  </si>
+  <si>
+    <t>bindu.k@esolutionpartners.com</t>
+  </si>
+  <si>
+    <t>bindu.priya@inspire-solutions.co.in</t>
+  </si>
+  <si>
+    <t>Binduhemkumar@gmail.com</t>
+  </si>
+  <si>
+    <t>binodini.panda@idctechnologies.com</t>
+  </si>
+  <si>
+    <t>bodegapradeepk@hexaware.com</t>
+  </si>
+  <si>
+    <t>bojamma@recruiseindia.com</t>
+  </si>
+  <si>
+    <t>bollu.shirisha@zencls.com</t>
+  </si>
+  <si>
+    <t>brindha@vrdella.com</t>
+  </si>
+  <si>
+    <t>brishti.chandra@ubique-systems.com</t>
+  </si>
+  <si>
+    <t>career@anviam.com</t>
+  </si>
+  <si>
+    <t>career@appstean.com</t>
+  </si>
+  <si>
+    <t>career@crystalvoxxltd.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Career@cyberkrits.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@fecundservices.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@geniuxtechsolution.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@gitakshmi.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@omexinfotech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@praeclarumtech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Career@programming.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@prowessiq.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@qaontop.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@quantixtech.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@scisglobal.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@sprybit.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@teamwebmark.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@utkallabs.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@utsahatechnologies.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">career@websenor.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careerconnect@resource-excellence.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers.allies15@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers.in@cogency.net </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@aapmor.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@alicorninfotech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@brownboxconsulting.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@bugsmirror.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@dreamsoft4u.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@gopazo.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@hr-hyre.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@kreedalabs.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@mentodesk.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@nasugroup.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@prglolinks.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@qualitrix.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@sidraforce.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@stitch.co </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@stitch.sa </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@surekhatech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@talentdivas.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@tetherfi.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@thebriminc.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@vervesquare.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@vkaps.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@xmatiq.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">careers@yanitsolutions.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chaitali.lad@dexian.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chaitanya.sahaya@qzigma.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chaitra@skygate.co.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandana.n@pisquaretech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandana.n@taltechs.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandini.tejawath@theaimatters.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandrashekhar.chakravarti@inextrix.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandrisha.desai@atyeti.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chandu.t@mlopssol.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">charan.kotikalapudi@teamlease.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CharanpreetK@selectsourceintl.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chathury1@galaxyitech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chavviimishra@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cheryl.sandhu@salesintel.io </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chhavi@ads247365.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chhaya.tomar@walkingtree.tech </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chigili.eurekha@cloudangles.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chippy.george@ellow.io </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chitra.Sharma@TalentOla.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">chitra.vgemperts@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">christan@globalitsearch.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ckeshoju@encore-c.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@axiotsystems.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@dakrishsolutions.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@enbridgeinfotech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@epochfolio.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@finstein.ai </t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@manorekha.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cramya@encore-c.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">cv@krmsystem.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">da@asanlabs.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dahabiya.p@codilar.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">danish@adescaretech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">darsana.vs@saasvaap.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dayanands@spanidea.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deeksha.s@lumbinielite.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deeksha@gudah.co.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepa@mmcindia.biz </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepak.sagrawal@ascendion.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepika.dheer@avencoree.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepika_birje@epam.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deepthi.pilli@gaallasoft.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deerdh.sheth@hitechdigital.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devaraj@trinityconsulting.asia </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devarapalli.amrutha@lovasit.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devika.chandana@xilligence.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devika.m@5datainc.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devika.rajesh.ballewar.tpr@pwc.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devikha_balu@epam.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devimahesh@cybaxistech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devindia@izoologic.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Devishree.Bakshi@xoriant.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">devyani.hire@ampcustech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhanalakshmi.p67@wipro.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhananjay.k@ampstek.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dhanashri.Y@bwbsol.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhanwantri.sharma@tdnewton.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dharanit@jnjsys.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dheeraj.kolani@cgi.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dheeraj.p@systechcorp.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dheerajmandal2023@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhivya@zen4techsolution.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhruvi.langaliya@cmarix.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dhruvsinghrao95.1@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digvijay.kumar_ext@ltts.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">digvijay@kk-talents.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">diksha.khandelwal@techsopi.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dimpy.sharma@solitaireinfotech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dineshwar.n01@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dinigasoftomatic@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dip.narayan@joulestowatts.co </t>
+  </si>
+  <si>
+    <t xml:space="preserve">director@peakhawks.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya.k@sureminds.co.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya.manhas@steelbazaar.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya.puthran@exazeit.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya.singh@thoughtworks.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya.vuthuri@dhruvaitsolutions.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divya@code-aspire.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">divyansh.chauhan@encora.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divyasri.l@alldigitech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dkvishwakarma143@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dudekula.rehana@teamlease.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">durgabhavani.p@firstmeridianglobal.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">dvarma@horizontal.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eathan2026@gmail.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">eera.rajashekar@in.experis.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">elakkiya.v@kej.co.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">elavarasi-r@hcltech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke.it@evokehr.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">farheen@s4ia.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">frithona@natobotics.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">gagana@nelson.net.in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ganapathi.bt@xanikainfotech.com </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ganesh.bandaru@inmar.com </t>
   </si>
 </sst>
 </file>
@@ -737,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A185"/>
+  <dimension ref="A1:A201"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
@@ -1349,196 +1589,404 @@
       </c>
     </row>
     <row r="122" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A122" s="2"/>
+      <c r="A122" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="123" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A123" s="2"/>
+      <c r="A123" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="124" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A124" s="2"/>
+      <c r="A124" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="125" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A125" s="2"/>
+      <c r="A125" s="2" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="126" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A126" s="2"/>
+      <c r="A126" s="2" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="127" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A127" s="2"/>
+      <c r="A127" s="2" t="s">
+        <v>126</v>
+      </c>
     </row>
     <row r="128" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A128" s="2"/>
+      <c r="A128" s="2" t="s">
+        <v>127</v>
+      </c>
     </row>
     <row r="129" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A129" s="2"/>
+      <c r="A129" s="2" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="130" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A130" s="2"/>
+      <c r="A130" s="2" t="s">
+        <v>129</v>
+      </c>
     </row>
     <row r="131" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A131" s="2"/>
+      <c r="A131" s="2" t="s">
+        <v>130</v>
+      </c>
     </row>
     <row r="132" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A132" s="2"/>
+      <c r="A132" s="2" t="s">
+        <v>131</v>
+      </c>
     </row>
     <row r="133" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A133" s="2"/>
+      <c r="A133" s="2" t="s">
+        <v>132</v>
+      </c>
     </row>
     <row r="134" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A134" s="2"/>
+      <c r="A134" s="2" t="s">
+        <v>133</v>
+      </c>
     </row>
     <row r="135" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A135" s="2"/>
+      <c r="A135" s="2" t="s">
+        <v>134</v>
+      </c>
     </row>
     <row r="136" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A136" s="2"/>
+      <c r="A136" s="2" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="137" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A137" s="2"/>
+      <c r="A137" s="2" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="138" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A138" s="2"/>
+      <c r="A138" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="139" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A139" s="2"/>
+      <c r="A139" s="2" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="140" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A140" s="2"/>
+      <c r="A140" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="141" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A141" s="2"/>
+      <c r="A141" s="2" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="142" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A142" s="2"/>
+      <c r="A142" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="143" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A143" s="2"/>
+      <c r="A143" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="144" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A144" s="2"/>
+      <c r="A144" s="2" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="145" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A145" s="2"/>
+      <c r="A145" s="2" t="s">
+        <v>144</v>
+      </c>
     </row>
     <row r="146" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A146" s="2"/>
+      <c r="A146" s="2" t="s">
+        <v>145</v>
+      </c>
     </row>
     <row r="147" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A147" s="2"/>
+      <c r="A147" s="2" t="s">
+        <v>146</v>
+      </c>
     </row>
     <row r="148" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A148" s="2"/>
+      <c r="A148" s="2" t="s">
+        <v>147</v>
+      </c>
     </row>
     <row r="149" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A149" s="2"/>
+      <c r="A149" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="150" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A150" s="2"/>
+      <c r="A150" s="2" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="151" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2"/>
+      <c r="A151" s="2" t="s">
+        <v>150</v>
+      </c>
     </row>
     <row r="152" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A152" s="2"/>
+      <c r="A152" s="2" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="153" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A153" s="2"/>
+      <c r="A153" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="154" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A154" s="2"/>
+      <c r="A154" s="2" t="s">
+        <v>153</v>
+      </c>
     </row>
     <row r="155" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A155" s="2"/>
+      <c r="A155" s="2" t="s">
+        <v>154</v>
+      </c>
     </row>
     <row r="156" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A156" s="2"/>
+      <c r="A156" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="157" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A157" s="2"/>
+      <c r="A157" s="2" t="s">
+        <v>156</v>
+      </c>
     </row>
     <row r="158" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2"/>
+      <c r="A158" s="2" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="159" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A159" s="2"/>
+      <c r="A159" s="2" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="160" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A160" s="2"/>
+      <c r="A160" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="161" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A161" s="2"/>
+      <c r="A161" s="2" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="162" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A162" s="2"/>
+      <c r="A162" s="2" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="163" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A163" s="2"/>
+      <c r="A163" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
     <row r="164" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A164" s="2"/>
+      <c r="A164" s="2" t="s">
+        <v>163</v>
+      </c>
     </row>
     <row r="165" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A165" s="2"/>
+      <c r="A165" s="2" t="s">
+        <v>164</v>
+      </c>
     </row>
     <row r="166" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A166" s="2"/>
+      <c r="A166" s="2" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="167" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A167" s="2"/>
+      <c r="A167" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="168" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A168" s="2"/>
+      <c r="A168" s="2" t="s">
+        <v>167</v>
+      </c>
     </row>
     <row r="169" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A169" s="2"/>
+      <c r="A169" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="170" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A170" s="2"/>
+      <c r="A170" s="2" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="171" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A171" s="2"/>
+      <c r="A171" s="2" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="172" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A172" s="2"/>
+      <c r="A172" s="2" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="173" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A173" s="2"/>
+      <c r="A173" s="2" t="s">
+        <v>172</v>
+      </c>
     </row>
     <row r="174" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A174" s="2"/>
+      <c r="A174" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
     <row r="175" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A175" s="2"/>
+      <c r="A175" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="176" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A176" s="2"/>
+      <c r="A176" s="2" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="177" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A177" s="2"/>
+      <c r="A177" s="2" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="178" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
+      <c r="A178" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="179" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A179" s="2"/>
+      <c r="A179" s="2" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="180" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A180" s="3"/>
+      <c r="A180" s="3" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="181" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A181" s="3"/>
+      <c r="A181" s="3" t="s">
+        <v>180</v>
+      </c>
     </row>
     <row r="182" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A182" s="3"/>
+      <c r="A182" s="3" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="183" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A183" s="3"/>
+      <c r="A183" s="3" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="184" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A184" s="3"/>
+      <c r="A184" s="3" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A185" s="3"/>
+      <c r="A185" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>200</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
